--- a/model_verification_output.xlsx
+++ b/model_verification_output.xlsx
@@ -482,7 +482,7 @@
         <v>202000</v>
       </c>
       <c r="D3" t="n">
-        <v>82.78700000000001</v>
+        <v>84.37</v>
       </c>
     </row>
     <row r="4">
@@ -496,7 +496,7 @@
         <v>202000</v>
       </c>
       <c r="D4" t="n">
-        <v>89.708</v>
+        <v>88.73999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -510,7 +510,7 @@
         <v>202000</v>
       </c>
       <c r="D5" t="n">
-        <v>94.2</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -524,7 +524,7 @@
         <v>202000</v>
       </c>
       <c r="D6" t="n">
-        <v>98</v>
+        <v>97.47</v>
       </c>
     </row>
     <row r="7">
@@ -538,7 +538,7 @@
         <v>202000</v>
       </c>
       <c r="D7" t="n">
-        <v>111.224</v>
+        <v>117.48</v>
       </c>
     </row>
     <row r="8">
@@ -552,7 +552,7 @@
         <v>202000</v>
       </c>
       <c r="D8" t="n">
-        <v>131.182</v>
+        <v>137.49</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         <v>202000</v>
       </c>
       <c r="D9" t="n">
-        <v>156.788</v>
+        <v>157.49</v>
       </c>
     </row>
     <row r="10">
@@ -580,7 +580,7 @@
         <v>202000</v>
       </c>
       <c r="D10" t="n">
-        <v>183.771</v>
+        <v>177.5</v>
       </c>
     </row>
     <row r="11">
@@ -594,7 +594,7 @@
         <v>202000</v>
       </c>
       <c r="D11" t="n">
-        <v>211.027</v>
+        <v>197.51</v>
       </c>
     </row>
     <row r="12">
@@ -608,7 +608,7 @@
         <v>202000</v>
       </c>
       <c r="D12" t="n">
-        <v>238.087</v>
+        <v>217.52</v>
       </c>
     </row>
     <row r="13">
@@ -622,7 +622,7 @@
         <v>202000</v>
       </c>
       <c r="D13" t="n">
-        <v>264.51</v>
+        <v>237.52</v>
       </c>
     </row>
     <row r="14">
@@ -636,7 +636,7 @@
         <v>202000</v>
       </c>
       <c r="D14" t="n">
-        <v>288.798</v>
+        <v>257.53</v>
       </c>
     </row>
     <row r="15">
@@ -650,7 +650,7 @@
         <v>202000</v>
       </c>
       <c r="D15" t="n">
-        <v>301</v>
+        <v>277.53</v>
       </c>
     </row>
     <row r="16">
@@ -664,7 +664,7 @@
         <v>202000</v>
       </c>
       <c r="D16" t="n">
-        <v>305.389</v>
+        <v>297.54</v>
       </c>
     </row>
     <row r="17">
@@ -678,7 +678,7 @@
         <v>202000</v>
       </c>
       <c r="D17" t="n">
-        <v>311.195</v>
+        <v>318.06</v>
       </c>
     </row>
     <row r="18">
@@ -692,7 +692,7 @@
         <v>202000</v>
       </c>
       <c r="D18" t="n">
-        <v>319.896</v>
+        <v>338.58</v>
       </c>
     </row>
     <row r="19">
@@ -706,7 +706,7 @@
         <v>202000</v>
       </c>
       <c r="D19" t="n">
-        <v>329.956</v>
+        <v>359.1</v>
       </c>
     </row>
     <row r="20">
@@ -720,7 +720,7 @@
         <v>202000</v>
       </c>
       <c r="D20" t="n">
-        <v>340.287</v>
+        <v>379.62</v>
       </c>
     </row>
     <row r="21">
@@ -734,7 +734,7 @@
         <v>202000</v>
       </c>
       <c r="D21" t="n">
-        <v>350.329</v>
+        <v>400.14</v>
       </c>
     </row>
     <row r="22">
@@ -748,7 +748,7 @@
         <v>202000</v>
       </c>
       <c r="D22" t="n">
-        <v>359.814</v>
+        <v>420.66</v>
       </c>
     </row>
     <row r="23">
@@ -762,7 +762,7 @@
         <v>202000</v>
       </c>
       <c r="D23" t="n">
-        <v>368.421</v>
+        <v>441.18</v>
       </c>
     </row>
     <row r="24">
@@ -776,7 +776,7 @@
         <v>202000</v>
       </c>
       <c r="D24" t="n">
-        <v>376.182</v>
+        <v>461.7</v>
       </c>
     </row>
     <row r="25">
@@ -790,7 +790,7 @@
         <v>202000</v>
       </c>
       <c r="D25" t="n">
-        <v>383.153</v>
+        <v>482.22</v>
       </c>
     </row>
     <row r="26">
@@ -804,7 +804,7 @@
         <v>202000</v>
       </c>
       <c r="D26" t="n">
-        <v>389.439</v>
+        <v>502.74</v>
       </c>
     </row>
   </sheetData>
